--- a/data/nzd0540/nzd0540.xlsx
+++ b/data/nzd0540/nzd0540.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O514"/>
+  <dimension ref="A1:O516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26614,10 +26614,10 @@
         <v>273.42</v>
       </c>
       <c r="C514" t="n">
-        <v>303.9</v>
+        <v>300.16</v>
       </c>
       <c r="D514" t="n">
-        <v>308.35</v>
+        <v>304.94</v>
       </c>
       <c r="E514" t="n">
         <v>305.57</v>
@@ -26652,6 +26652,108 @@
       <c r="O514" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>262.46</v>
+      </c>
+      <c r="C515" t="n">
+        <v>300.3</v>
+      </c>
+      <c r="D515" t="n">
+        <v>304.3</v>
+      </c>
+      <c r="E515" t="n">
+        <v>302.27</v>
+      </c>
+      <c r="F515" t="n">
+        <v>302.87</v>
+      </c>
+      <c r="G515" t="n">
+        <v>303.69</v>
+      </c>
+      <c r="H515" t="n">
+        <v>290.8</v>
+      </c>
+      <c r="I515" t="n">
+        <v>291.02</v>
+      </c>
+      <c r="J515" t="n">
+        <v>291.88</v>
+      </c>
+      <c r="K515" t="n">
+        <v>302.46</v>
+      </c>
+      <c r="L515" t="n">
+        <v>301.1</v>
+      </c>
+      <c r="M515" t="n">
+        <v>298.52</v>
+      </c>
+      <c r="N515" t="n">
+        <v>301.66</v>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>256.11</v>
+      </c>
+      <c r="C516" t="n">
+        <v>300.3</v>
+      </c>
+      <c r="D516" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="E516" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="F516" t="n">
+        <v>301.47</v>
+      </c>
+      <c r="G516" t="n">
+        <v>302.15</v>
+      </c>
+      <c r="H516" t="n">
+        <v>288.75</v>
+      </c>
+      <c r="I516" t="n">
+        <v>290.76</v>
+      </c>
+      <c r="J516" t="n">
+        <v>292.13</v>
+      </c>
+      <c r="K516" t="n">
+        <v>302.15</v>
+      </c>
+      <c r="L516" t="n">
+        <v>301.07</v>
+      </c>
+      <c r="M516" t="n">
+        <v>298.39</v>
+      </c>
+      <c r="N516" t="n">
+        <v>300.69</v>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26666,7 +26768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B524"/>
+  <dimension ref="A1:B526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31909,6 +32011,26 @@
       </c>
       <c r="B524" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -32077,28 +32199,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1563238418708315</v>
+        <v>0.1358901079863183</v>
       </c>
       <c r="J2" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K2" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001727225494736362</v>
+        <v>0.00131261975232333</v>
       </c>
       <c r="M2" t="n">
-        <v>20.48756105539616</v>
+        <v>20.50212382434326</v>
       </c>
       <c r="N2" t="n">
-        <v>759.7324693763061</v>
+        <v>759.3708631930325</v>
       </c>
       <c r="O2" t="n">
-        <v>27.56324489925499</v>
+        <v>27.55668454645864</v>
       </c>
       <c r="P2" t="n">
-        <v>280.9067389864961</v>
+        <v>281.1292143712967</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32159,28 +32281,28 @@
         <v>0.0368</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1686528458175405</v>
+        <v>-0.1646884058845322</v>
       </c>
       <c r="J3" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K3" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007943881165432654</v>
+        <v>0.00764087663287194</v>
       </c>
       <c r="M3" t="n">
-        <v>10.90465165798459</v>
+        <v>10.88017733025241</v>
       </c>
       <c r="N3" t="n">
-        <v>193.5837944899284</v>
+        <v>192.891656705801</v>
       </c>
       <c r="O3" t="n">
-        <v>13.91343934798037</v>
+        <v>13.88854408157317</v>
       </c>
       <c r="P3" t="n">
-        <v>297.8940873391868</v>
+        <v>297.851356176473</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32237,28 +32359,28 @@
         <v>0.0578</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.227454722592613</v>
+        <v>-0.224888823104202</v>
       </c>
       <c r="J4" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K4" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0238355965812943</v>
+        <v>0.02351392185580881</v>
       </c>
       <c r="M4" t="n">
-        <v>8.511020212608125</v>
+        <v>8.488827472745323</v>
       </c>
       <c r="N4" t="n">
-        <v>115.4688941721263</v>
+        <v>115.0107515207793</v>
       </c>
       <c r="O4" t="n">
-        <v>10.74564535856857</v>
+        <v>10.72430657528865</v>
       </c>
       <c r="P4" t="n">
-        <v>304.5257378550733</v>
+        <v>304.4980666091352</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32315,28 +32437,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1992958255439404</v>
+        <v>-0.1975350345684392</v>
       </c>
       <c r="J5" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K5" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02159759626336233</v>
+        <v>0.0214024179343999</v>
       </c>
       <c r="M5" t="n">
-        <v>7.584673541378006</v>
+        <v>7.561864148341651</v>
       </c>
       <c r="N5" t="n">
-        <v>98.05881624017879</v>
+        <v>97.69926037557454</v>
       </c>
       <c r="O5" t="n">
-        <v>9.902465159755867</v>
+        <v>9.884293620465478</v>
       </c>
       <c r="P5" t="n">
-        <v>304.6640583697852</v>
+        <v>304.6451109823684</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32393,28 +32515,28 @@
         <v>0.0502</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09949937885191849</v>
+        <v>-0.09983804194375011</v>
       </c>
       <c r="J6" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K6" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006017730027362389</v>
+        <v>0.006110882408079776</v>
       </c>
       <c r="M6" t="n">
-        <v>7.207823924961784</v>
+        <v>7.182851301264252</v>
       </c>
       <c r="N6" t="n">
-        <v>89.11787581326431</v>
+        <v>88.77441745930169</v>
       </c>
       <c r="O6" t="n">
-        <v>9.440226470443614</v>
+        <v>9.422017695764623</v>
       </c>
       <c r="P6" t="n">
-        <v>305.2627258162346</v>
+        <v>305.2663728866779</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32471,28 +32593,28 @@
         <v>0.0465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09655869654762492</v>
+        <v>0.09383883630801669</v>
       </c>
       <c r="J7" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K7" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006076953206883839</v>
+        <v>0.005787788042268094</v>
       </c>
       <c r="M7" t="n">
-        <v>6.829580872371726</v>
+        <v>6.817149679458583</v>
       </c>
       <c r="N7" t="n">
-        <v>83.10512504998496</v>
+        <v>82.83109728832049</v>
       </c>
       <c r="O7" t="n">
-        <v>9.116201240099132</v>
+        <v>9.101159117844302</v>
       </c>
       <c r="P7" t="n">
-        <v>303.8133836761941</v>
+        <v>303.8426574863198</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32549,28 +32671,28 @@
         <v>0.0384</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1565054216184233</v>
+        <v>0.1526085268059082</v>
       </c>
       <c r="J8" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K8" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01704608108897099</v>
+        <v>0.01633978316417772</v>
       </c>
       <c r="M8" t="n">
-        <v>6.863263858058995</v>
+        <v>6.855601350437145</v>
       </c>
       <c r="N8" t="n">
-        <v>76.97426161668233</v>
+        <v>76.77470045158012</v>
       </c>
       <c r="O8" t="n">
-        <v>8.773497684315094</v>
+        <v>8.762117349795089</v>
       </c>
       <c r="P8" t="n">
-        <v>290.574179770529</v>
+        <v>290.6161217284732</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32627,28 +32749,28 @@
         <v>0.054</v>
       </c>
       <c r="I9" t="n">
-        <v>0.30168657646166</v>
+        <v>0.2969055602745431</v>
       </c>
       <c r="J9" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K9" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07478219265099784</v>
+        <v>0.07302974796421946</v>
       </c>
       <c r="M9" t="n">
-        <v>6.218773752456517</v>
+        <v>6.219334915346712</v>
       </c>
       <c r="N9" t="n">
-        <v>61.3671438718071</v>
+        <v>61.27232635298649</v>
       </c>
       <c r="O9" t="n">
-        <v>7.833718393700855</v>
+        <v>7.82766416966048</v>
       </c>
       <c r="P9" t="n">
-        <v>288.9328034356751</v>
+        <v>288.9842573098952</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32705,28 +32827,28 @@
         <v>0.0694</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2071803233155857</v>
+        <v>0.2017754446282151</v>
       </c>
       <c r="J10" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K10" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05434731532561132</v>
+        <v>0.0518984643345487</v>
       </c>
       <c r="M10" t="n">
-        <v>4.981054660046303</v>
+        <v>4.990661110628495</v>
       </c>
       <c r="N10" t="n">
-        <v>40.70321620307099</v>
+        <v>40.72852490676974</v>
       </c>
       <c r="O10" t="n">
-        <v>6.37990722527146</v>
+        <v>6.381890386615062</v>
       </c>
       <c r="P10" t="n">
-        <v>293.373786253234</v>
+        <v>293.4319532801327</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32783,28 +32905,28 @@
         <v>0.0631</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2729699952079283</v>
+        <v>0.2687140285341501</v>
       </c>
       <c r="J11" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K11" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08849168631870941</v>
+        <v>0.08645897055836704</v>
       </c>
       <c r="M11" t="n">
-        <v>5.184124782856063</v>
+        <v>5.185866102067405</v>
       </c>
       <c r="N11" t="n">
-        <v>41.82790727762002</v>
+        <v>41.77922595562428</v>
       </c>
       <c r="O11" t="n">
-        <v>6.467449827994031</v>
+        <v>6.463685168355918</v>
       </c>
       <c r="P11" t="n">
-        <v>300.4483088393739</v>
+        <v>300.4941122073707</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32861,28 +32983,28 @@
         <v>0.0699</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3801639554666916</v>
+        <v>0.374485566281923</v>
       </c>
       <c r="J12" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K12" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1789737120077506</v>
+        <v>0.1750366610301528</v>
       </c>
       <c r="M12" t="n">
-        <v>4.616002037894851</v>
+        <v>4.627418854521555</v>
       </c>
       <c r="N12" t="n">
-        <v>36.18780565402531</v>
+        <v>36.2498044941831</v>
       </c>
       <c r="O12" t="n">
-        <v>6.015630112799931</v>
+        <v>6.020781053499878</v>
       </c>
       <c r="P12" t="n">
-        <v>298.1777820738066</v>
+        <v>298.2388701445806</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32939,28 +33061,28 @@
         <v>0.0607</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3383713797122569</v>
+        <v>0.3342573946025738</v>
       </c>
       <c r="J13" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K13" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1804104759334136</v>
+        <v>0.1775390843250994</v>
       </c>
       <c r="M13" t="n">
-        <v>3.989203624759946</v>
+        <v>3.992738840309536</v>
       </c>
       <c r="N13" t="n">
-        <v>28.39059194840881</v>
+        <v>28.3865892456102</v>
       </c>
       <c r="O13" t="n">
-        <v>5.328282269963633</v>
+        <v>5.327906647606563</v>
       </c>
       <c r="P13" t="n">
-        <v>294.6663279981138</v>
+        <v>294.7105863848826</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33017,28 +33139,28 @@
         <v>0.0305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3245302808830422</v>
+        <v>0.3180739643085774</v>
       </c>
       <c r="J14" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K14" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1309659606206452</v>
+        <v>0.1266562280017608</v>
       </c>
       <c r="M14" t="n">
-        <v>4.599051143174461</v>
+        <v>4.609439311334775</v>
       </c>
       <c r="N14" t="n">
-        <v>38.14532883631607</v>
+        <v>38.25998486351876</v>
       </c>
       <c r="O14" t="n">
-        <v>6.176190479277341</v>
+        <v>6.185465614124676</v>
       </c>
       <c r="P14" t="n">
-        <v>300.7547191647231</v>
+        <v>300.8241777427752</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33076,7 +33198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O514"/>
+  <dimension ref="A1:O516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72561,12 +72683,12 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>-46.46767049383831,169.75804415893126</t>
+          <t>-46.46764473051679,169.75801286944926</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>-46.46814168733302,169.7574004199854</t>
+          <t>-46.46812021259665,169.75736873866902</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -72622,6 +72744,160 @@
       <c r="O514" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-46.46697527357934,169.75840579435317</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-46.467645694919334,169.75801404071277</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-46.468116182146666,169.75736279261827</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-46.4686099010582,169.75674984972065</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-46.46913669049883,169.75622588579873</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-46.469702514989535,169.75573633925572</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-46.470290514065375,169.75524829659125</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-46.470899827199986,169.7550254851623</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-46.47147404117087,169.75477829235433</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-46.47211055417637,169.75460027051082</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-46.47276771237371,169.7544323105749</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>-46.47340159034231,169.754373037792</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>-46.47401622547381,169.75436738624202</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-46.466930548416954,169.75835441204018</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-46.467645694919334,169.75801404071277</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-46.46810497245616,169.7573462551693</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-46.46860223662713,169.75673588967578</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-46.46912950275182,169.7562109260984</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-46.46969616597036,169.75571852625612</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-46.47028461716749,169.75522301692817</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-46.47089912945665,169.75502225532614</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-46.47147480797446,169.75478135114628</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>-46.472109796541034,169.75459638748217</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-46.472767680297466,169.75443192286616</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>-46.473401511300544,169.75437134957056</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>-46.47401552695562,169.75435480102595</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0540/nzd0540.xlsx
+++ b/data/nzd0540/nzd0540.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O516"/>
+  <dimension ref="A1:O518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26662,7 +26662,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>262.46</v>
+        <v>273.42</v>
       </c>
       <c r="C515" t="n">
         <v>300.3</v>
@@ -26713,10 +26713,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>256.11</v>
+        <v>265.15</v>
       </c>
       <c r="C516" t="n">
-        <v>300.3</v>
+        <v>296.78</v>
       </c>
       <c r="D516" t="n">
         <v>302.52</v>
@@ -26754,6 +26754,108 @@
       <c r="O516" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>264.14</v>
+      </c>
+      <c r="C517" t="n">
+        <v>291.58</v>
+      </c>
+      <c r="D517" t="n">
+        <v>297.78</v>
+      </c>
+      <c r="E517" t="n">
+        <v>297.3</v>
+      </c>
+      <c r="F517" t="n">
+        <v>298.72</v>
+      </c>
+      <c r="G517" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="H517" t="n">
+        <v>285.99</v>
+      </c>
+      <c r="I517" t="n">
+        <v>289.11</v>
+      </c>
+      <c r="J517" t="n">
+        <v>291.21</v>
+      </c>
+      <c r="K517" t="n">
+        <v>301.65</v>
+      </c>
+      <c r="L517" t="n">
+        <v>301.4</v>
+      </c>
+      <c r="M517" t="n">
+        <v>297.52</v>
+      </c>
+      <c r="N517" t="n">
+        <v>299.98</v>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>257.47</v>
+      </c>
+      <c r="C518" t="n">
+        <v>288.18</v>
+      </c>
+      <c r="D518" t="n">
+        <v>295.17</v>
+      </c>
+      <c r="E518" t="n">
+        <v>295.52</v>
+      </c>
+      <c r="F518" t="n">
+        <v>296.97</v>
+      </c>
+      <c r="G518" t="n">
+        <v>298.01</v>
+      </c>
+      <c r="H518" t="n">
+        <v>285.35</v>
+      </c>
+      <c r="I518" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="J518" t="n">
+        <v>291.9</v>
+      </c>
+      <c r="K518" t="n">
+        <v>302.65</v>
+      </c>
+      <c r="L518" t="n">
+        <v>302.81</v>
+      </c>
+      <c r="M518" t="n">
+        <v>298.57</v>
+      </c>
+      <c r="N518" t="n">
+        <v>300.72</v>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32031,6 +32133,26 @@
       </c>
       <c r="B526" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -32199,28 +32321,28 @@
         <v>0.0362</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1358901079863183</v>
+        <v>0.1246710802945181</v>
       </c>
       <c r="J2" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K2" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00131261975232333</v>
+        <v>0.001113806090878411</v>
       </c>
       <c r="M2" t="n">
-        <v>20.50212382434326</v>
+        <v>20.47230454977719</v>
       </c>
       <c r="N2" t="n">
-        <v>759.3708631930325</v>
+        <v>757.1122352771561</v>
       </c>
       <c r="O2" t="n">
-        <v>27.55668454645864</v>
+        <v>27.51567253906682</v>
       </c>
       <c r="P2" t="n">
-        <v>281.1292143712967</v>
+        <v>281.2527935193322</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32281,28 +32403,28 @@
         <v>0.0368</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1646884058845322</v>
+        <v>-0.1688201288238596</v>
       </c>
       <c r="J3" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K3" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00764087663287194</v>
+        <v>0.008096826084402986</v>
       </c>
       <c r="M3" t="n">
-        <v>10.88017733025241</v>
+        <v>10.84650758675088</v>
       </c>
       <c r="N3" t="n">
-        <v>192.891656705801</v>
+        <v>192.1340831224262</v>
       </c>
       <c r="O3" t="n">
-        <v>13.88854408157317</v>
+        <v>13.8612439240649</v>
       </c>
       <c r="P3" t="n">
-        <v>297.851356176473</v>
+        <v>297.8960424251567</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32359,28 +32481,28 @@
         <v>0.0578</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.224888823104202</v>
+        <v>-0.2264315271727163</v>
       </c>
       <c r="J4" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K4" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02351392185580881</v>
+        <v>0.02403119006270549</v>
       </c>
       <c r="M4" t="n">
-        <v>8.488827472745323</v>
+        <v>8.464577480785623</v>
       </c>
       <c r="N4" t="n">
-        <v>115.0107515207793</v>
+        <v>114.5871559365373</v>
       </c>
       <c r="O4" t="n">
-        <v>10.72430657528865</v>
+        <v>10.70453903428528</v>
       </c>
       <c r="P4" t="n">
-        <v>304.4980666091352</v>
+        <v>304.5147922711673</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32437,28 +32559,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1975350345684392</v>
+        <v>-0.199823903116436</v>
       </c>
       <c r="J5" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K5" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0214024179343999</v>
+        <v>0.02207174017340419</v>
       </c>
       <c r="M5" t="n">
-        <v>7.561864148341651</v>
+        <v>7.546467394300199</v>
       </c>
       <c r="N5" t="n">
-        <v>97.69926037557454</v>
+        <v>97.35691088173678</v>
       </c>
       <c r="O5" t="n">
-        <v>9.884293620465478</v>
+        <v>9.866960569584576</v>
       </c>
       <c r="P5" t="n">
-        <v>304.6451109823684</v>
+        <v>304.6699179552136</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32515,28 +32637,28 @@
         <v>0.0502</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09983804194375011</v>
+        <v>-0.1035502543515742</v>
       </c>
       <c r="J6" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K6" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006110882408079776</v>
+        <v>0.006621842349282758</v>
       </c>
       <c r="M6" t="n">
-        <v>7.182851301264252</v>
+        <v>7.176365532114366</v>
       </c>
       <c r="N6" t="n">
-        <v>88.77441745930169</v>
+        <v>88.51963165611352</v>
       </c>
       <c r="O6" t="n">
-        <v>9.422017695764623</v>
+        <v>9.408487214005953</v>
       </c>
       <c r="P6" t="n">
-        <v>305.2663728866779</v>
+        <v>305.3066016289583</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32593,28 +32715,28 @@
         <v>0.0465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09383883630801669</v>
+        <v>0.08791186065954699</v>
       </c>
       <c r="J7" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K7" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005787788042268094</v>
+        <v>0.005114435582024068</v>
       </c>
       <c r="M7" t="n">
-        <v>6.817149679458583</v>
+        <v>6.821391955632062</v>
       </c>
       <c r="N7" t="n">
-        <v>82.83109728832049</v>
+        <v>82.7316810752616</v>
       </c>
       <c r="O7" t="n">
-        <v>9.101159117844302</v>
+        <v>9.095695744431078</v>
       </c>
       <c r="P7" t="n">
-        <v>303.8426574863198</v>
+        <v>303.906882543368</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32671,28 +32793,28 @@
         <v>0.0384</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1526085268059082</v>
+        <v>0.1455135520186756</v>
       </c>
       <c r="J8" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K8" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01633978316417772</v>
+        <v>0.01494705463377111</v>
       </c>
       <c r="M8" t="n">
-        <v>6.855601350437145</v>
+        <v>6.863012388112669</v>
       </c>
       <c r="N8" t="n">
-        <v>76.77470045158012</v>
+        <v>76.7913539073791</v>
       </c>
       <c r="O8" t="n">
-        <v>8.762117349795089</v>
+        <v>8.763067608285303</v>
       </c>
       <c r="P8" t="n">
-        <v>290.6161217284732</v>
+        <v>290.6929981595974</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32749,28 +32871,28 @@
         <v>0.054</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2969055602745431</v>
+        <v>0.2904848420121858</v>
       </c>
       <c r="J9" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K9" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07302974796421946</v>
+        <v>0.07042504575716746</v>
       </c>
       <c r="M9" t="n">
-        <v>6.219334915346712</v>
+        <v>6.228256804603279</v>
       </c>
       <c r="N9" t="n">
-        <v>61.27232635298649</v>
+        <v>61.2922712451159</v>
       </c>
       <c r="O9" t="n">
-        <v>7.82766416966048</v>
+        <v>7.828938066246016</v>
       </c>
       <c r="P9" t="n">
-        <v>288.9842573098952</v>
+        <v>289.0538283090393</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32827,28 +32949,28 @@
         <v>0.0694</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2017754446282151</v>
+        <v>0.1960496641432153</v>
       </c>
       <c r="J10" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K10" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0518984643345487</v>
+        <v>0.04931414098919817</v>
       </c>
       <c r="M10" t="n">
-        <v>4.990661110628495</v>
+        <v>5.001608154924425</v>
       </c>
       <c r="N10" t="n">
-        <v>40.72852490676974</v>
+        <v>40.77549626662957</v>
       </c>
       <c r="O10" t="n">
-        <v>6.381890386615062</v>
+        <v>6.385569376855096</v>
       </c>
       <c r="P10" t="n">
-        <v>293.4319532801327</v>
+        <v>293.4939892048101</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32905,28 +33027,28 @@
         <v>0.0631</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2687140285341501</v>
+        <v>0.2643481725786101</v>
       </c>
       <c r="J11" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K11" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08645897055836704</v>
+        <v>0.08436333192816947</v>
       </c>
       <c r="M11" t="n">
-        <v>5.185866102067405</v>
+        <v>5.187934870379745</v>
       </c>
       <c r="N11" t="n">
-        <v>41.77922595562428</v>
+        <v>41.73722456684784</v>
       </c>
       <c r="O11" t="n">
-        <v>6.463685168355918</v>
+        <v>6.460435323323641</v>
       </c>
       <c r="P11" t="n">
-        <v>300.4941122073707</v>
+        <v>300.5414121300274</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32983,28 +33105,28 @@
         <v>0.0699</v>
       </c>
       <c r="I12" t="n">
-        <v>0.374485566281923</v>
+        <v>0.3696166940204013</v>
       </c>
       <c r="J12" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K12" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1750366610301528</v>
+        <v>0.1719511832832264</v>
       </c>
       <c r="M12" t="n">
-        <v>4.627418854521555</v>
+        <v>4.634441570219881</v>
       </c>
       <c r="N12" t="n">
-        <v>36.2498044941831</v>
+        <v>36.25912771883526</v>
       </c>
       <c r="O12" t="n">
-        <v>6.020781053499878</v>
+        <v>6.021555257475868</v>
       </c>
       <c r="P12" t="n">
-        <v>298.2388701445806</v>
+        <v>298.2915998612804</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33061,28 +33183,28 @@
         <v>0.0607</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3342573946025738</v>
+        <v>0.3298227430551912</v>
       </c>
       <c r="J13" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K13" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1775390843250994</v>
+        <v>0.1743086831358907</v>
       </c>
       <c r="M13" t="n">
-        <v>3.992738840309536</v>
+        <v>3.997823576412624</v>
       </c>
       <c r="N13" t="n">
-        <v>28.3865892456102</v>
+        <v>28.40032550661103</v>
       </c>
       <c r="O13" t="n">
-        <v>5.327906647606563</v>
+        <v>5.329195577815758</v>
       </c>
       <c r="P13" t="n">
-        <v>294.7105863848826</v>
+        <v>294.7586144543449</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33139,28 +33261,28 @@
         <v>0.0305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3180739643085774</v>
+        <v>0.3109957112943081</v>
       </c>
       <c r="J14" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K14" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1266562280017608</v>
+        <v>0.1218263026101927</v>
       </c>
       <c r="M14" t="n">
-        <v>4.609439311334775</v>
+        <v>4.622665092217781</v>
       </c>
       <c r="N14" t="n">
-        <v>38.25998486351876</v>
+        <v>38.42479729338167</v>
       </c>
       <c r="O14" t="n">
-        <v>6.185465614124676</v>
+        <v>6.198773854028042</v>
       </c>
       <c r="P14" t="n">
-        <v>300.8241777427752</v>
+        <v>300.9008402265549</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33198,7 +33320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O516"/>
+  <dimension ref="A1:O518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72755,7 +72877,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>-46.46697527357934,169.75840579435317</t>
+          <t>-46.46705246845527,169.75849447961286</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -72832,12 +72954,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>-46.466930548416954,169.75835441204018</t>
+          <t>-46.466994220137785,169.758427561059</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>-46.467645694919334,169.75801404071277</t>
+          <t>-46.46762144708036,169.7579845918143</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -72898,6 +73020,160 @@
       <c r="O516" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-46.466987106374646,169.7584193884279</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-46.467585626396314,169.7579410878074</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-46.46807512192108,169.7573022172766</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-46.468582096508584,169.75669920636508</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-46.46911538395761,169.75618154098433</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-46.46968565297817,169.75568903071422</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-46.47027667792077,169.7551889818787</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-46.470894701467905,169.7550017582911</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-46.47147198613687,169.7547700947924</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>-46.47210857454829,169.754590124533</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>-46.472768033136056,169.75443618766252</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>-46.473400982327995,169.75436005147318</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>-46.474015015668236,169.75434558916703</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-46.466940127351144,169.758365416749</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-46.467562205171554,169.75791264291053</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-46.46805868522727,169.7572779685841</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-46.46857213833476,169.756681068516</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-46.46910639926662,169.7561628413743</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-46.46967909781464,169.7556706393822</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-46.4702748369346,169.7551810896948</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-46.47089293027141,169.75499355947804</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-46.47147410251516,169.7547785370577</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>-46.47211101853344,169.75460265043168</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>-46.472769540717316,169.75445440997498</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>-46.473401620743005,169.75437368710797</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>-46.474015548559294,169.75435519025942</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
